--- a/resultados/resultados_RS_cv_vs_test.xlsx
+++ b/resultados/resultados_RS_cv_vs_test.xlsx
@@ -1,20 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos_D\etapa-analisis_pcsmote\resultados\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DAB164-82FC-43A5-8CEF-2694379085D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$1</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="34">
   <si>
     <t>tecnica</t>
   </si>
@@ -88,10 +97,28 @@
     <t>025</t>
   </si>
   <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
     <t>030</t>
   </si>
   <si>
     <t>Upp040</t>
+  </si>
+  <si>
+    <t>Upp045</t>
+  </si>
+  <si>
+    <t>Upp050</t>
+  </si>
+  <si>
+    <t>Upp060</t>
   </si>
   <si>
     <t>0</t>
@@ -103,8 +130,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,12 +156,107 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="12">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -144,8 +266,23 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
@@ -156,10 +293,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -167,13 +322,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -211,7 +374,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -245,6 +408,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -279,9 +443,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -454,427 +619,594 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="6">
+        <v>11600</v>
+      </c>
+      <c r="K2" s="6">
+        <v>255361</v>
+      </c>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6">
+        <v>208961</v>
+      </c>
+      <c r="N2" s="6">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="O2" s="7">
+        <v>0.95199999999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="6">
+        <v>11600</v>
+      </c>
+      <c r="K3" s="6">
+        <v>218854</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6">
+        <v>172454</v>
+      </c>
+      <c r="N3" s="6">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="O3" s="7">
+        <v>0.95199999999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="6">
+        <v>11600</v>
+      </c>
+      <c r="K4" s="6">
+        <v>255283</v>
+      </c>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6">
+        <v>208883</v>
+      </c>
+      <c r="N4" s="6">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="O4" s="7">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="6">
+        <v>70</v>
+      </c>
+      <c r="D5" s="6">
+        <v>30</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="6">
+        <v>11600</v>
+      </c>
+      <c r="K5" s="6">
+        <v>182363</v>
+      </c>
+      <c r="L5" s="6">
+        <v>6756</v>
+      </c>
+      <c r="M5" s="6">
+        <v>135963</v>
+      </c>
+      <c r="N5" s="6">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="O5" s="7">
+        <v>0.85699999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2">
+      <c r="C6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="9">
         <v>11600</v>
       </c>
-      <c r="K2">
+      <c r="K6" s="9">
         <v>46400</v>
       </c>
-      <c r="N2">
-        <v>0.963</v>
-      </c>
-      <c r="O2">
-        <v>0.855</v>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="O6" s="10">
+        <v>0.85499999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
-      <c r="A3" t="s">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="3">
+        <v>11600</v>
+      </c>
+      <c r="K7" s="3">
+        <v>252763</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3">
+        <v>206831</v>
+      </c>
+      <c r="N7" s="3">
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0.99099999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="6">
+        <v>11600</v>
+      </c>
+      <c r="K8" s="6">
+        <v>216663</v>
+      </c>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6">
+        <v>170731</v>
+      </c>
+      <c r="N8" s="6">
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="O8" s="7">
+        <v>0.99099999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="6">
+        <v>11600</v>
+      </c>
+      <c r="K9" s="6">
+        <v>252728</v>
+      </c>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6">
+        <v>206796</v>
+      </c>
+      <c r="N9" s="6">
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="O9" s="7">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="6">
+        <v>70</v>
+      </c>
+      <c r="D10" s="6">
+        <v>30</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="6">
+        <v>11600</v>
+      </c>
+      <c r="K10" s="6">
+        <v>252728</v>
+      </c>
+      <c r="L10" s="6">
+        <v>7685</v>
+      </c>
+      <c r="M10" s="6">
+        <v>206796</v>
+      </c>
+      <c r="N10" s="6">
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="O10" s="7">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="6">
+        <v>70</v>
+      </c>
+      <c r="D11" s="6">
+        <v>30</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="6">
+        <v>11600</v>
+      </c>
+      <c r="K11" s="6">
+        <v>252728</v>
+      </c>
+      <c r="L11" s="6">
+        <v>7105</v>
+      </c>
+      <c r="M11" s="6">
+        <v>206796</v>
+      </c>
+      <c r="N11" s="6">
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="O11" s="7">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="6">
+        <v>70</v>
+      </c>
+      <c r="D12" s="6">
+        <v>30</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="6">
+        <v>11600</v>
+      </c>
+      <c r="K12" s="6">
+        <v>252728</v>
+      </c>
+      <c r="L12" s="6">
+        <v>7105</v>
+      </c>
+      <c r="M12" s="6">
+        <v>206796</v>
+      </c>
+      <c r="N12" s="6">
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="O12" s="7">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3">
+      <c r="C13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="9">
         <v>11600</v>
       </c>
-      <c r="K3">
+      <c r="K13" s="9">
         <v>45932</v>
       </c>
-      <c r="N3">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="O3">
-        <v>0.831</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4">
-        <v>11600</v>
-      </c>
-      <c r="K4">
-        <v>255361</v>
-      </c>
-      <c r="M4">
-        <v>208961</v>
-      </c>
-      <c r="N4">
-        <v>0.963</v>
-      </c>
-      <c r="O4">
-        <v>0.952</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5">
-        <v>11600</v>
-      </c>
-      <c r="K5">
-        <v>252763</v>
-      </c>
-      <c r="M5">
-        <v>206831</v>
-      </c>
-      <c r="N5">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="O5">
-        <v>0.991</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6">
-        <v>11600</v>
-      </c>
-      <c r="K6">
-        <v>218854</v>
-      </c>
-      <c r="M6">
-        <v>172454</v>
-      </c>
-      <c r="N6">
-        <v>0.963</v>
-      </c>
-      <c r="O6">
-        <v>0.952</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7">
-        <v>11600</v>
-      </c>
-      <c r="K7">
-        <v>216663</v>
-      </c>
-      <c r="M7">
-        <v>170731</v>
-      </c>
-      <c r="N7">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="O7">
-        <v>0.991</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8">
-        <v>11600</v>
-      </c>
-      <c r="K8">
-        <v>255283</v>
-      </c>
-      <c r="M8">
-        <v>208883</v>
-      </c>
-      <c r="N8">
-        <v>0.963</v>
-      </c>
-      <c r="O8">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9">
-        <v>11600</v>
-      </c>
-      <c r="K9">
-        <v>252728</v>
-      </c>
-      <c r="M9">
-        <v>206796</v>
-      </c>
-      <c r="N9">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="O9">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10">
-        <v>70</v>
-      </c>
-      <c r="D10">
-        <v>30</v>
-      </c>
-      <c r="E10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10">
-        <v>11600</v>
-      </c>
-      <c r="K10">
-        <v>252728</v>
-      </c>
-      <c r="L10">
-        <v>7685</v>
-      </c>
-      <c r="M10">
-        <v>206796</v>
-      </c>
-      <c r="N10">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="O10">
-        <v>0.95</v>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9">
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="O13" s="10">
+        <v>0.83099999999999996</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O13">
+      <sortCondition ref="I1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/resultados/resultados_RS_cv_vs_test.xlsx
+++ b/resultados/resultados_RS_cv_vs_test.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3362,7 +3362,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>20</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>21</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
@@ -3627,7 +3627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
@@ -3680,7 +3680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>23</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>23</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>23</v>
       </c>
@@ -3857,7 +3857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
@@ -3967,7 +3967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>19</v>
       </c>
@@ -4022,7 +4022,7 @@
   <autoFilter ref="A1:S13">
     <filterColumn colId="8">
       <filters>
-        <filter val="0"/>
+        <filter val="1"/>
       </filters>
     </filterColumn>
     <sortState ref="A4:S12">
